--- a/BOOKING_RESULT_Brasov_05-15-2026_000000_07-20-2026_000000_3_guests.xlsx
+++ b/BOOKING_RESULT_Brasov_05-15-2026_000000_07-20-2026_000000_3_guests.xlsx
@@ -19,241 +19,295 @@
     <x:t>HotelName</x:t>
   </x:si>
   <x:si>
-    <x:t>Url</x:t>
+    <x:t>HotelUrl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rating</x:t>
   </x:si>
   <x:si>
     <x:t>Price</x:t>
   </x:si>
   <x:si>
-    <x:t>Rating</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central houses budget friendly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/central-houses-budget-friendly.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1407467402_412519025_0_0_0&amp;highlighted_blocks=1407467402_412519025_0_0_0&amp;matching_block_id=1407467402_412519025_0_0_0&amp;sr_pri_blocks=1407467402_412519025_0_0_0__70206&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>702 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YamaLuxe Luxury Apartments - București</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/yamaluxe-apartments-bucuresti.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1171951105_389727277_2_2_0&amp;highlighted_blocks=1171951105_389727277_2_2_0&amp;matching_block_id=1171951105_389727277_2_2_0&amp;sr_pri_blocks=1171951105_389727277_2_2_0__61435&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
+    <x:t>https://www.booking.com/hotel/ro/white-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=559451708_209413944_0_0_0&amp;highlighted_blocks=559451708_209413944_0_0_0&amp;matching_block_id=559451708_209413944_0_0_0&amp;sr_pri_blocks=559451708_209413944_0_0_0__1537547&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGI studio CORESI &amp; parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,375 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,193 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bark Inn - Bed and Breakfast</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/bark-inn-bed-and-breakfast.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1320902003_404782112_0_1_0&amp;highlighted_blocks=1320902003_404782112_0_1_0&amp;matching_block_id=1320902003_404782112_0_1_0&amp;sr_pri_blocks=1320902003_404782112_0_1_0__3046050&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51,879 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament Racadau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-racadau-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=749019701_331158284_3_0_0&amp;highlighted_blocks=749019701_331158284_3_0_0&amp;matching_block_id=749019701_331158284_3_0_0&amp;sr_pri_blocks=749019701_331158284_3_0_0__1488816&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,279 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-aparthotel-1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=995130006_405288024_4_0_0&amp;highlighted_blocks=995130006_405288024_4_0_0&amp;matching_block_id=995130006_405288024_4_0_0&amp;sr_pri_blocks=995130006_405288024_4_0_0__3084939&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select City Center Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/historical-center-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31850708_421755992_3_0_0&amp;highlighted_blocks=31850708_421755992_3_0_0&amp;matching_block_id=31850708_421755992_3_0_0&amp;sr_pri_blocks=31850708_421755992_3_0_0__2585682&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,857 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,050 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pension Bavaria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pension-bavaria.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31458704_246256401_3_0_0&amp;highlighted_blocks=31458704_246256401_3_0_0&amp;matching_block_id=31458704_246256401_3_0_0&amp;sr_pri_blocks=31458704_246256401_3_0_0__1971000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,710 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73,128 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TampaView ApartHotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/tampaview-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1422457001_423999646_0_0_0&amp;highlighted_blocks=1422457001_423999646_0_0_0&amp;matching_block_id=1422457001_423999646_0_0_0&amp;sr_pri_blocks=1422457001_423999646_0_0_0__3605000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/luca-brasov2.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1348675301_408707859_0_0_0&amp;highlighted_blocks=1348675301_408707859_0_0_0&amp;matching_block_id=1348675301_408707859_0_0_0&amp;sr_pri_blocks=1348675301_408707859_0_0_0__1287000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,870 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,853 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Davino Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-davino-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1094405206_382349208_4_0_0_877326&amp;highlighted_blocks=1094405206_382349208_4_0_0_877326&amp;matching_block_id=1094405206_382349208_4_0_0_877326&amp;sr_pri_blocks=1094405206_382349208_4_0_0_877326_2571956&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,720 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Nest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-nest-brasov20.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1324188501_425784292_4_0_0&amp;highlighted_blocks=1324188501_425784292_4_0_0&amp;matching_block_id=1324188501_425784292_4_0_0&amp;sr_pri_blocks=1324188501_425784292_4_0_0__4051944&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Luxury Apartments Kasper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-confortable-promenada-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1109165407_383666009_3_0_0_337045&amp;highlighted_blocks=1109165407_383666009_3_0_0_337045&amp;matching_block_id=1109165407_383666009_3_0_0_337045&amp;sr_pri_blocks=1109165407_383666009_3_0_0_337045_2323200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Memo Haus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-memo-haus.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1395631202_411470735_4_0_0&amp;highlighted_blocks=1395631202_411470735_4_0_0&amp;matching_block_id=1395631202_411470735_4_0_0&amp;sr_pri_blocks=1395631202_411470735_4_0_0__3344279&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,321 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skylark Central Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/skylark-geneva-suite-with-fireplace-amp-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1117857507_384637893_3_0_0&amp;highlighted_blocks=1117857507_384637893_3_0_0&amp;matching_block_id=1117857507_384637893_3_0_0&amp;sr_pri_blocks=1117857507_384637893_3_0_0__3465000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,650 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEAK Aparthotel - Old Town - by CityHost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/peak-aparthotel-by-cityhost.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1166912003_389307937_3_0_0&amp;highlighted_blocks=1166912003_389307937_3_0_0&amp;matching_block_id=1166912003_389307937_3_0_0&amp;sr_pri_blocks=1166912003_389307937_3_0_0__2975419&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,044 lei29,754 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Comfortable Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-isaran.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=969942706_369395472_3_0_0_337069&amp;highlighted_blocks=969942706_369395472_3_0_0_337069&amp;matching_block_id=969942706_369395472_3_0_0_337069&amp;sr_pri_blocks=969942706_369395472_3_0_0_337069_2185260&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Roth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-roth-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=251825904_222711381_3_0_0&amp;highlighted_blocks=251825904_222711381_3_0_0&amp;matching_block_id=251825904_222711381_3_0_0&amp;sr_pri_blocks=251825904_222711381_3_0_0__1927930&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pensiunea Leo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pensiunea-leo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=34116103_264837064_3_0_0&amp;highlighted_blocks=34116103_264837064_3_0_0&amp;matching_block_id=34116103_264837064_3_0_0&amp;sr_pri_blocks=34116103_264837064_3_0_0__2178000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,780 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mandala Designer Apartments with Free Private Parking, near Mall Coresi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/mandala-a-designer-penthouse-with-free-private-parking-near-mall-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=929406402_364926508_5_0_0&amp;highlighted_blocks=929406402_364926508_5_0_0&amp;matching_block_id=929406402_364926508_5_0_0&amp;sr_pri_blocks=929406402_364926508_5_0_0__7312800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Sunlight Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sunlight-apartment-by-taboo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=806763501_360416925_4_0_0&amp;highlighted_blocks=806763501_360416925_4_0_0&amp;matching_block_id=806763501_360416925_4_0_0&amp;sr_pri_blocks=806763501_360416925_4_0_0__2564430&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,644 lei</x:t>
   </x:si>
   <x:si>
     <x:t>9.0</x:t>
   </x:si>
   <x:si>
-    <x:t>Bucharest Central C Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/old-town-bohemian-attic.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1052035601_399555355_2_0_0&amp;highlighted_blocks=1052035601_399555355_2_0_0&amp;matching_block_id=1052035601_399555355_2_0_0&amp;sr_pri_blocks=1052035601_399555355_2_0_0__62428&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>624 lei</x:t>
+    <x:t>Bb's Cosy Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/bb-39-s-cosy-apartments-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=295908503_329654120_0_0_0&amp;highlighted_blocks=295908503_329654120_0_0_0&amp;matching_block_id=295908503_329654120_0_0_0&amp;sr_pri_blocks=295908503_329654120_0_0_0__2194500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,080 lei21,945 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warm Amber Suites Brașov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cosmopolit-lifestyle.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=282931413_126032420_3_0_0_677855&amp;highlighted_blocks=282931413_126032420_3_0_0_677855&amp;matching_block_id=282931413_126032420_3_0_0_677855&amp;sr_pri_blocks=282931413_126032420_3_0_0_677855_3132080&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coresi Mall Area Studios &amp; Apartments by GLAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/coresi-mall-area-studios-amp-apartments-by-glam.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1118248102_412223809_3_0_0&amp;highlighted_blocks=1118248102_412223809_3_0_0&amp;matching_block_id=1118248102_412223809_3_0_0&amp;sr_pri_blocks=1118248102_412223809_3_0_0__2877300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,773 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Old Town View &amp; Balcony Apartments MM Host</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/brasov-old-town-with-mountain-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1428222201_417107964_3_0_0&amp;highlighted_blocks=1428222201_417107964_3_0_0&amp;matching_block_id=1428222201_417107964_3_0_0&amp;sr_pri_blocks=1428222201_417107964_3_0_0__5187930&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,993 lei16,263 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main Square Apartments &amp; More</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/main-square-apartments-amp-more.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=116190210_208743329_0_0_0&amp;highlighted_blocks=116190210_208743329_0_0_0&amp;matching_block_id=116190210_208743329_0_0_0&amp;sr_pri_blocks=116190210_208743329_0_0_0__1626341&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Città Studi Suites - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bb-too-cute-2b-str8.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKRoarKBsACAdICJDZmMGU5Mzc2LTJjYjgtNGRiMy05NWI0LWRhYmUwZjRkYzUzYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=26&amp;hapos=26&amp;sr_order=popularity&amp;srpvid=d0bf5a9436ca15d7&amp;srepoch=1766494379&amp;all_sr_blocks=120214214_373646928_1_0_0&amp;highlighted_blocks=120214214_373646928_1_0_0&amp;matching_block_id=120214214_373646928_1_0_0&amp;sr_pri_blocks=120214214_373646928_1_0_0__43850&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>8.9</x:t>
   </x:si>
   <x:si>
-    <x:t>Piața Romană Zone Apartament</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/piata-romana-zone-apartament.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1517819701_423491097_2_0_0&amp;highlighted_blocks=1517819701_423491097_2_0_0&amp;matching_block_id=1517819701_423491097_2_0_0&amp;sr_pri_blocks=1517819701_423491097_2_0_0__59700&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The City Retreat Apart-Hotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/the-city-retreat-apart.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1332711703_405777882_2_0_0_913798&amp;highlighted_blocks=1332711703_405777882_2_0_0_913798&amp;matching_block_id=1332711703_405777882_2_0_0_913798&amp;sr_pri_blocks=1332711703_405777882_2_0_0_913798_76837&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>768 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Old City Calea Victoriei Deluxe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/old-city-calea-victoriei-deluxe.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1504909701_422237916_2_0_0&amp;highlighted_blocks=1504909701_422237916_2_0_0&amp;matching_block_id=1504909701_422237916_2_0_0&amp;sr_pri_blocks=1504909701_422237916_2_0_0__76150&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Home Guest - Apartment 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/home-guest-apartments-bucuresti1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1385508701_414901259_2_0_0&amp;highlighted_blocks=1385508701_414901259_2_0_0&amp;matching_block_id=1385508701_414901259_2_0_0&amp;sr_pri_blocks=1385508701_414901259_2_0_0__45900&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central Residence Apartment 812 B3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/central-residence-apartment-812.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1144452501_387298811_2_0_0_561427&amp;highlighted_blocks=1144452501_387298811_2_0_0_561427&amp;matching_block_id=1144452501_387298811_2_0_0_561427&amp;sr_pri_blocks=1144452501_387298811_2_0_0_561427_62000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>620 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arena Park</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/arena-park.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1392496305_411201441_2_0_0_1164546&amp;highlighted_blocks=1392496305_411201441_2_0_0_1164546&amp;matching_block_id=1392496305_411201441_2_0_0_1164546&amp;sr_pri_blocks=1392496305_411201441_2_0_0_1164546_67500&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central Residence Studio P25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/central-residence-studio-p25.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1268463001_399568933_2_0_0_603269&amp;highlighted_blocks=1268463001_399568933_2_0_0_603269&amp;matching_block_id=1268463001_399568933_2_0_0_603269&amp;sr_pri_blocks=1268463001_399568933_2_0_0_603269_62000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AT Central Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/at-central-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=503858904_408972632_2_0_0_521942&amp;highlighted_blocks=503858904_408972632_2_0_0_521942&amp;matching_block_id=503858904_408972632_2_0_0_521942&amp;sr_pri_blocks=503858904_408972632_2_0_0_521942_96000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>960 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pura Vida Downtown Tiny houses</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/downtown-tiny-houses-near-cismigiu-gardens.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1289267905_401875389_2_0_0_750797&amp;highlighted_blocks=1289267905_401875389_2_0_0_750797&amp;matching_block_id=1289267905_401875389_2_0_0_750797&amp;sr_pri_blocks=1289267905_401875389_2_0_0_750797_57335&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>573 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Upground Residence Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/upground-residence-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=460874901_0_2_0_0&amp;highlighted_blocks=460874901_0_2_0_0&amp;matching_block_id=460874901_0_2_0_0&amp;sr_pri_blocks=460874901_0_2_0_0__84302&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>365 Apartments in Bucharest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/365-apartments-in-bucharest.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1089796301_381884070_2_0_0&amp;highlighted_blocks=1089796301_381884070_2_0_0&amp;matching_block_id=1089796301_381884070_2_0_0&amp;sr_pri_blocks=1089796301_381884070_2_0_0__121784&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Riviera Unirii Residence</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/riviera-unirii-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=927007703_383045109_0_2_0&amp;highlighted_blocks=927007703_383045109_0_2_0&amp;matching_block_id=927007703_383045109_0_2_0&amp;sr_pri_blocks=927007703_383045109_0_2_0__57000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crystal Palace Hotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/crystal-palace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=4116105_141318468_2_2_0_590627&amp;highlighted_blocks=4116105_141318468_2_2_0_590627&amp;matching_block_id=4116105_141318468_2_2_0_590627&amp;sr_pri_blocks=4116105_141318468_2_2_0_590627_167642&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ultimate Living Experience - Modern Accommodation &amp; Free Parking near Romexpo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/two-bedroom-apartment-with-free-parking.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=769352802_334675763_2_0_0&amp;highlighted_blocks=769352802_334675763_2_0_0&amp;matching_block_id=769352802_334675763_2_0_0&amp;sr_pri_blocks=769352802_334675763_2_0_0__93670&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>937 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HIGHLINE DOWNTOWN ApartHotel OLDTOWN UNIRII SQUARE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/highline-downtown.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=550833714_200909667_2_0_0&amp;highlighted_blocks=550833714_200909667_2_0_0&amp;matching_block_id=550833714_200909667_2_0_0&amp;sr_pri_blocks=550833714_200909667_2_0_0__104438&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,044 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Downtown Terrace Nest Victoriei Gara de Nord</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/downtown-terrace-nest-victory-gara-de-nord.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1470621701_418410430_2_0_0&amp;highlighted_blocks=1470621701_418410430_2_0_0&amp;matching_block_id=1470621701_418410430_2_0_0&amp;sr_pri_blocks=1470621701_418410430_2_0_0__173400&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One by One - by Grand Accommodation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bucharest-check-in.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=224642942_413845015_2_0_0&amp;highlighted_blocks=224642942_413845015_2_0_0&amp;matching_block_id=224642942_413845015_2_0_0&amp;sr_pri_blocks=224642942_413845015_2_0_0__108000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wonderful Apartments in Prime North Location - Heaven for Extended Stays</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/wonderful-1br-amp-balcony-heaven-for-extended-stays.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1061440001_378456007_2_0_0&amp;highlighted_blocks=1061440001_378456007_2_0_0&amp;matching_block_id=1061440001_378456007_2_0_0&amp;sr_pri_blocks=1061440001_378456007_2_0_0__124270&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,243 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomis Garden Bucuresti</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/tomis-garden-bucuresti.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__137193&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bucharest Premium Luxury Studios &amp; Apartments by Glam Story</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bucharest-premium-luxury-studios-amp-apartments-by-glam-story.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1337095501_412223728_2_0_0&amp;highlighted_blocks=1337095501_412223728_2_0_0&amp;matching_block_id=1337095501_412223728_2_0_0&amp;sr_pri_blocks=1337095501_412223728_2_0_0__110000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bright and cozy apartment in the Bucharest center</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bright-and-cozy-apartment-in-the-bucharest-center.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=1357898201_408129470_2_0_0&amp;highlighted_blocks=1357898201_408129470_2_0_0&amp;matching_block_id=1357898201_408129470_2_0_0&amp;sr_pri_blocks=1357898201_408129470_2_0_0__58320&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROSETTI Hotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/rosetti-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=304c7af7f14d7d22b74caeec5251d628&amp;srepoch=1766488749&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__122275&amp;from=searchresults</x:t>
+    <x:t>2,231 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brasov Gondola Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/mgi-studio-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1413131701_413051882_0_0_0&amp;highlighted_blocks=1413131701_413051882_0_0_0&amp;matching_block_id=1413131701_413051882_0_0_0&amp;sr_pri_blocks=1413131701_413051882_0_0_0__1119300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,461 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,888 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,849 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,519 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23,232 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,443 lei</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -604,7 +658,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D26"/>
+  <x:dimension ref="A1:C26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -623,128 +677,128 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="C9" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
@@ -755,24 +809,24 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -786,7 +840,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
@@ -797,178 +851,192 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/BOOKING_RESULT_Brasov_05-15-2026_000000_07-20-2026_000000_3_guests.xlsx
+++ b/BOOKING_RESULT_Brasov_05-15-2026_000000_07-20-2026_000000_3_guests.xlsx
@@ -28,286 +28,1864 @@
     <x:t>Price</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/ro/white-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=559451708_209413944_0_0_0&amp;highlighted_blocks=559451708_209413944_0_0_0&amp;matching_block_id=559451708_209413944_0_0_0&amp;sr_pri_blocks=559451708_209413944_0_0_0__1537547&amp;from=searchresults</x:t>
+    <x:t>TampaView ApartHotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/bark-inn-bed-and-breakfast.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1320902003_404782112_0_1_0&amp;highlighted_blocks=1320902003_404782112_0_1_0&amp;matching_block_id=1320902003_404782112_0_1_0&amp;sr_pri_blocks=1320902003_404782112_0_1_0__3039966&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38,426</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bark Inn - Bed and Breakfast</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-aparthotel-1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=995130006_405288024_4_0_0&amp;highlighted_blocks=995130006_405288024_4_0_0&amp;matching_block_id=995130006_405288024_4_0_0&amp;sr_pri_blocks=995130006_405288024_4_0_0__3075744&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/historical-center-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=31850708_417813236_3_0_0&amp;highlighted_blocks=31850708_417813236_3_0_0&amp;matching_block_id=31850708_417813236_3_0_0&amp;sr_pri_blocks=31850708_417813236_3_0_0__2823150&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,757</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select City Center Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Luxury Apartments Kasper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-confortable-promenada-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1109165405_383666009_3_0_0_337045&amp;highlighted_blocks=1109165405_383666009_3_0_0_337045&amp;matching_block_id=1109165405_383666009_3_0_0_337045&amp;sr_pri_blocks=1109165405_383666009_3_0_0_337045_2430078&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Davino Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-davino-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1094405206_382349208_4_0_0_877326&amp;highlighted_blocks=1094405206_382349208_4_0_0_877326&amp;matching_block_id=1094405206_382349208_4_0_0_877326&amp;sr_pri_blocks=1094405206_382349208_4_0_0_877326_2603800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,819</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,038</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Memo Haus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-memo-haus.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1395631202_411470735_4_0_0&amp;highlighted_blocks=1395631202_411470735_4_0_0&amp;matching_block_id=1395631202_411470735_4_0_0&amp;sr_pri_blocks=1395631202_411470735_4_0_0__3581879&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ArtMob Apartment Isaran</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/artmob-isaran.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1107133401_383497084_0_0_0_1082260&amp;highlighted_blocks=1107133401_383497084_0_0_0_1082260&amp;matching_block_id=1107133401_383497084_0_0_0_1082260&amp;sr_pri_blocks=1107133401_383497084_0_0_0_1082260_5680600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,806</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEAK Aparthotel - Old Town - by CityHost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/peak-aparthotel-by-cityhost.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1166912003_389307937_3_0_0&amp;highlighted_blocks=1166912003_389307937_3_0_0&amp;matching_block_id=1166912003_389307937_3_0_0&amp;sr_pri_blocks=1166912003_389307937_3_0_0__3064993&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,650</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Roth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-roth-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=251825904_222711381_3_0_0&amp;highlighted_blocks=251825904_222711381_3_0_0&amp;matching_block_id=251825904_222711381_3_0_0&amp;sr_pri_blocks=251825904_222711381_3_0_0__1922613&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/main-square-apartments-amp-more.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=116190210_208743329_0_0_0&amp;highlighted_blocks=116190210_208743329_0_0_0&amp;matching_block_id=116190210_208743329_0_0_0&amp;sr_pri_blocks=116190210_208743329_0_0_0__1648541&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main Square Apartments &amp; More</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dynamic Nest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,485</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/dynamic-nest.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1376419302_414561215_3_0_0&amp;highlighted_blocks=1376419302_414561215_3_0_0&amp;matching_block_id=1376419302_414561215_3_0_0&amp;sr_pri_blocks=1376419302_414561215_3_0_0__2502557&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mandala Designer Apartments with Free Private Parking, near Mall Coresi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/mandala-a-designer-penthouse-with-free-private-parking-near-mall-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=929406402_364926508_5_0_0&amp;highlighted_blocks=929406402_364926508_5_0_0&amp;matching_block_id=929406402_364926508_5_0_0&amp;sr_pri_blocks=929406402_364926508_5_0_0__7326300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ONE66 - Luxury Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/one66.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1391861902_411156230_3_0_0_1199065&amp;highlighted_blocks=1391861902_411156230_3_0_0_1199065&amp;matching_block_id=1391861902_411156230_3_0_0_1199065&amp;sr_pri_blocks=1391861902_411156230_3_0_0_1199065_6138634&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61,386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Luxury 3 Rooms Apartments Urban Plaza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-premium-apartments-urban.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1010271609_373728155_3_0_0_337048&amp;highlighted_blocks=1010271609_373728155_3_0_0_337048&amp;matching_block_id=1010271609_373728155_3_0_0_337048&amp;sr_pri_blocks=1010271609_373728155_3_0_0_337048_2583821&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,838</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coresi Mall Area Studios &amp; Apartments by GLAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/coresi-mall-area-studios-amp-apartments-by-glam.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1118248101_412223809_3_0_0&amp;highlighted_blocks=1118248101_412223809_3_0_0&amp;matching_block_id=1118248101_412223809_3_0_0&amp;sr_pri_blocks=1118248101_412223809_3_0_0__2593950&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,940</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Old Town View &amp; Balcony Apartments MM Host</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/brasov-old-town-with-mountain-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1428222201_417107964_3_0_0&amp;highlighted_blocks=1428222201_417107964_3_0_0&amp;matching_block_id=1428222201_417107964_3_0_0&amp;sr_pri_blocks=1428222201_417107964_3_0_0__5619008&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Curtea Brasoveana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/curtea-brasoveana.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=17945506_221329989_3_1_0_424225&amp;highlighted_blocks=17945506_221329989_3_1_0_424225&amp;matching_block_id=17945506_221329989_3_1_0_424225&amp;sr_pri_blocks=17945506_221329989_3_1_0_424225_3999600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,996</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Comfortable Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-isaran.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=969942706_369395472_3_0_0_337069&amp;highlighted_blocks=969942706_369395472_3_0_0_337069&amp;matching_block_id=969942706_369395472_3_0_0_337069&amp;sr_pri_blocks=969942706_369395472_3_0_0_337069_2248039&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,480</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brasov Gondola Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/white-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=559451705_209413944_0_0_0&amp;highlighted_blocks=559451705_209413944_0_0_0&amp;matching_block_id=559451705_209413944_0_0_0&amp;sr_pri_blocks=559451705_209413944_0_0_0__1702800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warm Amber Suites Brașov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cosmopolit-lifestyle.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=282931413_126032420_3_0_0_677855&amp;highlighted_blocks=282931413_126032420_3_0_0_677855&amp;matching_block_id=282931413_126032420_3_0_0_677855&amp;sr_pri_blocks=282931413_126032420_3_0_0_677855_3119114&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,191</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Balcescu</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pensiunea-balcescu.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=116912312_174127817_3_0_0&amp;highlighted_blocks=116912312_174127817_3_0_0&amp;matching_block_id=116912312_174127817_3_0_0&amp;sr_pri_blocks=116912312_174127817_3_0_0__2910600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Art Gallery Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/art-galery-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=545096801_295664144_0_0_0&amp;highlighted_blocks=545096801_295664144_0_0_0&amp;matching_block_id=545096801_295664144_0_0_0&amp;sr_pri_blocks=545096801_295664144_0_0_0__2950638&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Muresenilor 9 Boutique - Old Town</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/muresenilor-9.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1324526603_405092771_3_0_0&amp;highlighted_blocks=1324526603_405092771_3_0_0&amp;matching_block_id=1324526603_405092771_3_0_0&amp;sr_pri_blocks=1324526603_405092771_3_0_0__4525100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,251</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Sunset Penthouse</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/maurer-residence-penthouse-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=717760601_360416929_6_0_0_1186466&amp;highlighted_blocks=717760601_360416929_6_0_0_1186466&amp;matching_block_id=717760601_360416929_6_0_0_1186466&amp;sr_pri_blocks=717760601_360416929_6_0_0_1186466_6064974&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60,650</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ylly aparts</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/tampaview-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1422457001_423999646_0_0_0&amp;highlighted_blocks=1422457001_423999646_0_0_0&amp;matching_block_id=1422457001_423999646_0_0_0&amp;sr_pri_blocks=1422457001_423999646_0_0_0__3842600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73,263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,506</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ylly-aparts.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=26&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=1125362403_385219703_3_0_0_699883&amp;highlighted_blocks=1125362403_385219703_3_0_0_699883&amp;matching_block_id=1125362403_385219703_3_0_0_699883&amp;sr_pri_blocks=1125362403_385219703_3_0_0_699883_5326315&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53,263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ka'yana Apartments - Restored Luxury in the Heart of the Old Town, near Black Church, Council Sq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ka-39-yana.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=27&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=758098902_332812635_3_0_0&amp;highlighted_blocks=758098902_332812635_3_0_0&amp;matching_block_id=758098902_332812635_3_0_0&amp;sr_pri_blocks=758098902_332812635_3_0_0__4560080&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hirscher Loft</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/residence-hirscher.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=28&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=17867216_126030229_3_0_0_426125&amp;highlighted_blocks=17867216_126030229_3_0_0_426125&amp;matching_block_id=17867216_126030229_3_0_0_426125&amp;sr_pri_blocks=17867216_126030229_3_0_0_426125_3504600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Moritz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-moritz.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=29&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=232599002_128933218_3_2_0_426314&amp;highlighted_blocks=232599002_128933218_3_2_0_426314&amp;matching_block_id=232599002_128933218_3_2_0_426314&amp;sr_pri_blocks=232599002_128933218_3_2_0_426314_3930255&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,303</x:t>
   </x:si>
   <x:si>
     <x:t>MGI studio CORESI &amp; parking</x:t>
   </x:si>
   <x:si>
-    <x:t>15,375 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,193 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bark Inn - Bed and Breakfast</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bark-inn-bed-and-breakfast.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1320902003_404782112_0_1_0&amp;highlighted_blocks=1320902003_404782112_0_1_0&amp;matching_block_id=1320902003_404782112_0_1_0&amp;sr_pri_blocks=1320902003_404782112_0_1_0__3046050&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51,879 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apartament Racadau</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/apartament-racadau-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=749019701_331158284_3_0_0&amp;highlighted_blocks=749019701_331158284_3_0_0&amp;matching_block_id=749019701_331158284_3_0_0&amp;sr_pri_blocks=749019701_331158284_3_0_0__1488816&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,279 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Aparthotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-aparthotel-1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=995130006_405288024_4_0_0&amp;highlighted_blocks=995130006_405288024_4_0_0&amp;matching_block_id=995130006_405288024_4_0_0&amp;sr_pri_blocks=995130006_405288024_4_0_0__3084939&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Select City Center Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/historical-center-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31850708_421755992_3_0_0&amp;highlighted_blocks=31850708_421755992_3_0_0&amp;matching_block_id=31850708_421755992_3_0_0&amp;sr_pri_blocks=31850708_421755992_3_0_0__2585682&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,857 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,050 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pension Bavaria</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/pension-bavaria.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31458704_246256401_3_0_0&amp;highlighted_blocks=31458704_246256401_3_0_0&amp;matching_block_id=31458704_246256401_3_0_0&amp;sr_pri_blocks=31458704_246256401_3_0_0__1971000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,710 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73,128 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TampaView ApartHotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/tampaview-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1422457001_423999646_0_0_0&amp;highlighted_blocks=1422457001_423999646_0_0_0&amp;matching_block_id=1422457001_423999646_0_0_0&amp;sr_pri_blocks=1422457001_423999646_0_0_0__3605000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.9</x:t>
+    <x:t>https://www.booking.com/hotel/ro/mgi-studio-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=30&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=1413131701_413051882_0_0_0&amp;highlighted_blocks=1413131701_413051882_0_0_0&amp;matching_block_id=1413131701_413051882_0_0_0&amp;sr_pri_blocks=1413131701_413051882_0_0_0__1267356&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,674</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bb's Cosy Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/bb-39-s-cosy-apartments-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=31&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=295908503_329654120_0_0_0&amp;highlighted_blocks=295908503_329654120_0_0_0&amp;matching_block_id=295908503_329654120_0_0_0&amp;sr_pri_blocks=295908503_329654120_0_0_0__2256540&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Sunlight Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sunlight-apartment-by-taboo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=32&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=806763501_360416925_4_0_0&amp;highlighted_blocks=806763501_360416925_4_0_0&amp;matching_block_id=806763501_360416925_4_0_0&amp;sr_pri_blocks=806763501_360416925_4_0_0__2596876&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Apollonia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apollonia.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=33&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=32641112_129960997_0_2_0&amp;highlighted_blocks=32641112_129960997_0_2_0&amp;matching_block_id=32641112_129960997_0_2_0&amp;sr_pri_blocks=32641112_129960997_0_2_0__3731200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37,312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Lais</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-lily-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=34&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=237998201_406744437_3_0_0&amp;highlighted_blocks=237998201_406744437_3_0_0&amp;matching_block_id=237998201_406744437_3_0_0&amp;sr_pri_blocks=237998201_406744437_3_0_0__3477600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Alley by Kanopian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/the-alley.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=35&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=777168003_336025042_0_2_0_853347&amp;highlighted_blocks=777168003_336025042_0_2_0_853347&amp;matching_block_id=777168003_336025042_0_2_0_853347&amp;sr_pri_blocks=777168003_336025042_0_2_0_853347_6099610&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60,996</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luxury 2 bedroom holiday apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/luxury-2-bedroom-holiday-apartment-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=36&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=890460201_359115049_0_0_0&amp;highlighted_blocks=890460201_359115049_0_0_0&amp;matching_block_id=890460201_359115049_0_0_0&amp;sr_pri_blocks=890460201_359115049_0_0_0__4725600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47,256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elegant Sophia's Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/elegant-sophia-39-s-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=37&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=436130901_145173291_4_0_0&amp;highlighted_blocks=436130901_145173291_4_0_0&amp;matching_block_id=436130901_145173291_4_0_0&amp;sr_pri_blocks=436130901_145173291_4_0_0__3848490&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38,485</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Cranta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-cranta.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=38&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=4607605_178126435_3_2_0&amp;highlighted_blocks=4607605_178126435_3_2_0&amp;matching_block_id=4607605_178126435_3_2_0&amp;sr_pri_blocks=4607605_178126435_3_2_0__4762300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47,623</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piata's Hidden Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/izzys-hidden-apartment-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=39&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=1025217001_377147403_0_0_0&amp;highlighted_blocks=1025217001_377147403_0_0_0&amp;matching_block_id=1025217001_377147403_0_0_0&amp;sr_pri_blocks=1025217001_377147403_0_0_0__1997575&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Noua Oasis BNB with PARKING</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-oasis-bnb.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=40&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=1054131503_377599004_3_0_0_718478&amp;highlighted_blocks=1054131503_377599004_3_0_0_718478&amp;matching_block_id=1054131503_377599004_3_0_0_718478&amp;sr_pri_blocks=1054131503_377599004_3_0_0_718478_1962554&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,626</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Graef</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-graef.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=41&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=204190902_216431038_4_0_0&amp;highlighted_blocks=204190902_216431038_4_0_0&amp;matching_block_id=204190902_216431038_4_0_0&amp;sr_pri_blocks=204190902_216431038_4_0_0__3463800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,638</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Richter Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/richter-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=42&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=980470404_370994378_3_0_0&amp;highlighted_blocks=980470404_370994378_3_0_0&amp;matching_block_id=980470404_370994378_3_0_0&amp;sr_pri_blocks=980470404_370994378_3_0_0__3568440&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,684</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Belfort Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/belfort-hotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=43&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=4740913_129959805_3_1_0_495792&amp;highlighted_blocks=4740913_129959805_3_1_0_495792&amp;matching_block_id=4740913_129959805_3_1_0_495792&amp;sr_pri_blocks=4740913_129959805_3_1_0_495792_6646200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66,462</x:t>
   </x:si>
   <x:si>
     <x:t>Luca</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/ro/luca-brasov2.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1348675301_408707859_0_0_0&amp;highlighted_blocks=1348675301_408707859_0_0_0&amp;matching_block_id=1348675301_408707859_0_0_0&amp;sr_pri_blocks=1348675301_408707859_0_0_0__1287000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,870 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21,853 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Davino Aparthotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-davino-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1094405206_382349208_4_0_0_877326&amp;highlighted_blocks=1094405206_382349208_4_0_0_877326&amp;matching_block_id=1094405206_382349208_4_0_0_877326&amp;sr_pri_blocks=1094405206_382349208_4_0_0_877326_2571956&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,720 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Nest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-nest-brasov20.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1324188501_425784292_4_0_0&amp;highlighted_blocks=1324188501_425784292_4_0_0&amp;matching_block_id=1324188501_425784292_4_0_0&amp;sr_pri_blocks=1324188501_425784292_4_0_0__4051944&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JAD Luxury Apartments Kasper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/jad-confortable-promenada-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1109165407_383666009_3_0_0_337045&amp;highlighted_blocks=1109165407_383666009_3_0_0_337045&amp;matching_block_id=1109165407_383666009_3_0_0_337045&amp;sr_pri_blocks=1109165407_383666009_3_0_0_337045_2323200&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Memo Haus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-memo-haus.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1395631202_411470735_4_0_0&amp;highlighted_blocks=1395631202_411470735_4_0_0&amp;matching_block_id=1395631202_411470735_4_0_0&amp;sr_pri_blocks=1395631202_411470735_4_0_0__3344279&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31,321 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skylark Central Aparthotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/skylark-geneva-suite-with-fireplace-amp-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1117857507_384637893_3_0_0&amp;highlighted_blocks=1117857507_384637893_3_0_0&amp;matching_block_id=1117857507_384637893_3_0_0&amp;sr_pri_blocks=1117857507_384637893_3_0_0__3465000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,650 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEAK Aparthotel - Old Town - by CityHost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/peak-aparthotel-by-cityhost.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1166912003_389307937_3_0_0&amp;highlighted_blocks=1166912003_389307937_3_0_0&amp;matching_block_id=1166912003_389307937_3_0_0&amp;sr_pri_blocks=1166912003_389307937_3_0_0__2975419&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33,044 lei29,754 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JAD Comfortable Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/jad-isaran.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=969942706_369395472_3_0_0_337069&amp;highlighted_blocks=969942706_369395472_3_0_0_337069&amp;matching_block_id=969942706_369395472_3_0_0_337069&amp;sr_pri_blocks=969942706_369395472_3_0_0_337069_2185260&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Casa Roth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/casa-roth-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=251825904_222711381_3_0_0&amp;highlighted_blocks=251825904_222711381_3_0_0&amp;matching_block_id=251825904_222711381_3_0_0&amp;sr_pri_blocks=251825904_222711381_3_0_0__1927930&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pensiunea Leo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/pensiunea-leo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=34116103_264837064_3_0_0&amp;highlighted_blocks=34116103_264837064_3_0_0&amp;matching_block_id=34116103_264837064_3_0_0&amp;sr_pri_blocks=34116103_264837064_3_0_0__2178000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21,780 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mandala Designer Apartments with Free Private Parking, near Mall Coresi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/mandala-a-designer-penthouse-with-free-private-parking-near-mall-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=929406402_364926508_5_0_0&amp;highlighted_blocks=929406402_364926508_5_0_0&amp;matching_block_id=929406402_364926508_5_0_0&amp;sr_pri_blocks=929406402_364926508_5_0_0__7312800&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Sunlight Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/sunlight-apartment-by-taboo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=806763501_360416925_4_0_0&amp;highlighted_blocks=806763501_360416925_4_0_0&amp;matching_block_id=806763501_360416925_4_0_0&amp;sr_pri_blocks=806763501_360416925_4_0_0__2564430&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,644 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bb's Cosy Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bb-39-s-cosy-apartments-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=295908503_329654120_0_0_0&amp;highlighted_blocks=295908503_329654120_0_0_0&amp;matching_block_id=295908503_329654120_0_0_0&amp;sr_pri_blocks=295908503_329654120_0_0_0__2194500&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,080 lei21,945 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warm Amber Suites Brașov</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/cosmopolit-lifestyle.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=282931413_126032420_3_0_0_677855&amp;highlighted_blocks=282931413_126032420_3_0_0_677855&amp;matching_block_id=282931413_126032420_3_0_0_677855&amp;sr_pri_blocks=282931413_126032420_3_0_0_677855_3132080&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Coresi Mall Area Studios &amp; Apartments by GLAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/coresi-mall-area-studios-amp-apartments-by-glam.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1118248102_412223809_3_0_0&amp;highlighted_blocks=1118248102_412223809_3_0_0&amp;matching_block_id=1118248102_412223809_3_0_0&amp;sr_pri_blocks=1118248102_412223809_3_0_0__2877300&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28,773 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Old Town View &amp; Balcony Apartments MM Host</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/brasov-old-town-with-mountain-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1428222201_417107964_3_0_0&amp;highlighted_blocks=1428222201_417107964_3_0_0&amp;matching_block_id=1428222201_417107964_3_0_0&amp;sr_pri_blocks=1428222201_417107964_3_0_0__5187930&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,993 lei16,263 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main Square Apartments &amp; More</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/main-square-apartments-amp-more.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=116190210_208743329_0_0_0&amp;highlighted_blocks=116190210_208743329_0_0_0&amp;matching_block_id=116190210_208743329_0_0_0&amp;sr_pri_blocks=116190210_208743329_0_0_0__1626341&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Città Studi Suites - Top Collection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bb-too-cute-2b-str8.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKRoarKBsACAdICJDZmMGU5Mzc2LTJjYjgtNGRiMy05NWI0LWRhYmUwZjRkYzUzYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=26&amp;hapos=26&amp;sr_order=popularity&amp;srpvid=d0bf5a9436ca15d7&amp;srepoch=1766494379&amp;all_sr_blocks=120214214_373646928_1_0_0&amp;highlighted_blocks=120214214_373646928_1_0_0&amp;matching_block_id=120214214_373646928_1_0_0&amp;sr_pri_blocks=120214214_373646928_1_0_0__43850&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,231 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brasov Gondola Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/mgi-studio-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1413131701_413051882_0_0_0&amp;highlighted_blocks=1413131701_413051882_0_0_0&amp;matching_block_id=1413131701_413051882_0_0_0&amp;sr_pri_blocks=1413131701_413051882_0_0_0__1119300&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30,461 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,888 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30,849 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,519 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23,232 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33,443 lei</x:t>
+    <x:t>https://www.booking.com/hotel/ro/luca-brasov2.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=44&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=1348675301_408707859_0_0_0&amp;highlighted_blocks=1348675301_408707859_0_0_0&amp;matching_block_id=1348675301_408707859_0_0_0&amp;sr_pri_blocks=1348675301_408707859_0_0_0__1421640&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,216</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Imperia Luxury Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/imperia-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=45&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=1108097803_383576086_0_1_0_893617&amp;highlighted_blocks=1108097803_383576086_0_1_0_893617&amp;matching_block_id=1108097803_383576086_0_1_0_893617&amp;sr_pri_blocks=1108097803_383576086_0_1_0_893617_20697600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>206,976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Monte Verde</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-monte-verde.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=46&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=31977507_128927550_3_2_0&amp;highlighted_blocks=31977507_128927550_3_2_0&amp;matching_block_id=31977507_128927550_3_2_0&amp;sr_pri_blocks=31977507_128927550_3_2_0__2908308&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Middle Penthouse</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/middle-penthouse.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=47&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=1243863201_396311736_0_0_0&amp;highlighted_blocks=1243863201_396311736_0_0_0&amp;matching_block_id=1243863201_396311736_0_0_0&amp;sr_pri_blocks=1243863201_396311736_0_0_0__3747285&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37,473</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vila William’s</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/vila-williams.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=48&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=435337304_147308954_0_0_0_874904&amp;highlighted_blocks=435337304_147308954_0_0_0_874904&amp;matching_block_id=435337304_147308954_0_0_0_874904&amp;sr_pri_blocks=435337304_147308954_0_0_0_874904_2914560&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Mureșan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-muresan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=49&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=4137714_128926762_0_2_0&amp;highlighted_blocks=4137714_128926762_0_2_0&amp;matching_block_id=4137714_128926762_0_2_0&amp;sr_pri_blocks=4137714_128926762_0_2_0__2806056&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,061</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coban Residence Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/a1-bohemian-apartment-in-city-center-by-coban-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=50&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896496&amp;all_sr_blocks=934591902_365695616_0_0_0&amp;highlighted_blocks=934591902_365695616_0_0_0&amp;matching_block_id=934591902_365695616_0_0_0&amp;sr_pri_blocks=934591902_365695616_0_0_0__3473850&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,739</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coresi Area Luxury GAP Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/coresi-area-luxury-gap-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=51&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1393641101_412223680_3_0_0&amp;highlighted_blocks=1393641101_412223680_3_0_0&amp;matching_block_id=1393641101_412223680_3_0_0&amp;sr_pri_blocks=1393641101_412223680_3_0_0__2558300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,583</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4FriendsBrasov K1256</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/4friendsbrasov-k1256.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=52&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1332115501_405725468_4_0_0_1210728&amp;highlighted_blocks=1332115501_405725468_4_0_0_1210728&amp;matching_block_id=1332115501_405725468_4_0_0_1210728&amp;sr_pri_blocks=1332115501_405725468_4_0_0_1210728_5076900&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50,769</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4FriendsBrasov K34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/4friendsbrasov-k34.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=53&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1357437203_408081647_4_0_0_1210726&amp;highlighted_blocks=1357437203_408081647_4_0_0_1210726&amp;matching_block_id=1357437203_408081647_4_0_0_1210726&amp;sr_pri_blocks=1357437203_408081647_4_0_0_1210726_5076900&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa V</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/villa-v.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=54&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=494739902_418528934_3_1_0&amp;highlighted_blocks=494739902_418528934_3_1_0&amp;matching_block_id=494739902_418528934_3_1_0&amp;sr_pri_blocks=494739902_418528934_3_1_0__5290800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52,908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brasov Holiday Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/brasov-holiday-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=55&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=209593612_361972181_3_2_0_901802&amp;highlighted_blocks=209593612_361972181_3_2_0_901802&amp;matching_block_id=209593612_361972181_3_2_0_901802&amp;sr_pri_blocks=209593612_361972181_3_2_0_901802_3674750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,748</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Almir Brașov Vila</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/almir.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=56&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1330088905_405718787_0_0_0&amp;highlighted_blocks=1330088905_405718787_0_0_0&amp;matching_block_id=1330088905_405718787_0_0_0&amp;sr_pri_blocks=1330088905_405718787_0_0_0__14687600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>146,876</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOYSO LIFE&amp;SPA Brasov Apartments - Couples Only</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-cu-gradina-in-brasov-b-house.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=57&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=839123201_350404869_3_0_0&amp;highlighted_blocks=839123201_350404869_3_0_0&amp;matching_block_id=839123201_350404869_3_0_0&amp;sr_pri_blocks=839123201_350404869_3_0_0__4300560&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cozy Apartment in Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cozy-apartment-in-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=58&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=438310801_397054427_4_0_0&amp;highlighted_blocks=438310801_397054427_4_0_0&amp;matching_block_id=438310801_397054427_4_0_0&amp;sr_pri_blocks=438310801_397054427_4_0_0__3692275&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,923</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Family Apartments &amp; Studios Calea Bucuresti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=59&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=867683901_355243938_3_0_0_337099&amp;highlighted_blocks=867683901_355243938_3_0_0_337099&amp;matching_block_id=867683901_355243938_3_0_0_337099&amp;sr_pri_blocks=867683901_355243938_3_0_0_337099_1863378&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,634</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palazzo Brașov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/palazzo-old-town.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=60&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=674945304_275845462_3_0_0&amp;highlighted_blocks=674945304_275845462_3_0_0&amp;matching_block_id=674945304_275845462_3_0_0&amp;sr_pri_blocks=674945304_275845462_3_0_0__2400750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,008</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Epic rooms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/epic-rooms.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=61&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1292265606_402177179_0_0_0_746958&amp;highlighted_blocks=1292265606_402177179_0_0_0_746958&amp;matching_block_id=1292265606_402177179_0_0_0_746958&amp;sr_pri_blocks=1292265606_402177179_0_0_0_746958_2807065&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,071</x:t>
+  </x:si>
+  <x:si>
+    <x:t>The Pines Boutique Villa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/the-pines-boutique-villa.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=62&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=195468103_126035955_4_1_0_570467&amp;highlighted_blocks=195468103_126035955_4_1_0_570467&amp;matching_block_id=195468103_126035955_4_1_0_570467&amp;sr_pri_blocks=195468103_126035955_4_1_0_570467_8322900&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83,229</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KUDO - Mountain &amp; Skyline view</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/kudo-mountain-amp-skyline-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=63&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1320009801_404705071_3_0_0&amp;highlighted_blocks=1320009801_404705071_3_0_0&amp;matching_block_id=1320009801_404705071_3_0_0&amp;sr_pri_blocks=1320009801_404705071_3_0_0__3495400&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,954</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M&amp;F Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/m-amp-f-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=64&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=265743401_234427140_6_0_0&amp;highlighted_blocks=265743401_234427140_6_0_0&amp;matching_block_id=265743401_234427140_6_0_0&amp;sr_pri_blocks=265743401_234427140_6_0_0__2605680&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Happy Mood Apartment 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/happy-mood-apartment-5.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=65&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=881543202_357423556_3_0_0&amp;highlighted_blocks=881543202_357423556_3_0_0&amp;matching_block_id=881543202_357423556_3_0_0&amp;sr_pri_blocks=881543202_357423556_3_0_0__2424613&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,246</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Lucan Brașov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-lucan-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=66&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=946529101_367197461_6_0_0&amp;highlighted_blocks=946529101_367197461_6_0_0&amp;matching_block_id=946529101_367197461_6_0_0&amp;sr_pri_blocks=946529101_367197461_6_0_0__11039100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>110,391</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBERT RESIDENCE Brasov Historical City Center</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/albert-residence-brasov-brasov1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=67&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1479899101_419613519_3_1_0&amp;highlighted_blocks=1479899101_419613519_3_1_0&amp;matching_block_id=1479899101_419613519_3_1_0&amp;sr_pri_blocks=1479899101_419613519_3_1_0__5840921&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,409</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Relax in Style Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/villa-in-style.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=68&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=791352814_417023336_3_0_0_869436&amp;highlighted_blocks=791352814_417023336_3_0_0_869436&amp;matching_block_id=791352814_417023336_3_0_0_869436&amp;sr_pri_blocks=791352814_417023336_3_0_0_869436_5652600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,526</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cosmopolit-booking.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=69&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1342181401_406614298_3_0_0&amp;highlighted_blocks=1342181401_406614298_3_0_0&amp;matching_block_id=1342181401_406614298_3_0_0&amp;sr_pri_blocks=1342181401_406614298_3_0_0__3416720&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,167</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MK Apartments Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/mk-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=70&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=649862008_265978214_3_0_0&amp;highlighted_blocks=649862008_265978214_3_0_0&amp;matching_block_id=649862008_265978214_3_0_0&amp;sr_pri_blocks=649862008_265978214_3_0_0__5386500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53,865</x:t>
+  </x:si>
+  <x:si>
+    <x:t>City Tales Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/comfy-apartment-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=71&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1059517501_381057595_4_0_0&amp;highlighted_blocks=1059517501_381057595_4_0_0&amp;matching_block_id=1059517501_381057595_4_0_0&amp;sr_pri_blocks=1059517501_381057595_4_0_0__4803030&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48,030</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Serenity Mountain Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/serenity-mountain-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=72&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1197632101_392057512_4_0_0&amp;highlighted_blocks=1197632101_392057512_4_0_0&amp;matching_block_id=1197632101_392057512_4_0_0&amp;sr_pri_blocks=1197632101_392057512_4_0_0__3079204&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,792</x:t>
+  </x:si>
+  <x:si>
+    <x:t>White Dream Penthouse with Jacuzzi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/white-dream-penthouse-with-jacuzzi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=73&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=812147101_343997528_4_0_0&amp;highlighted_blocks=812147101_343997528_4_0_0&amp;matching_block_id=812147101_343997528_4_0_0&amp;sr_pri_blocks=812147101_343997528_4_0_0__6202600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>62,026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>premium suites Postavarului</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/old-town-postavarului-46.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=74&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=479256601_377807219_3_0_0&amp;highlighted_blocks=479256601_377807219_3_0_0&amp;matching_block_id=479256601_377807219_3_0_0&amp;sr_pri_blocks=479256601_377807219_3_0_0__4231200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vila Sas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/vila-sas.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=75&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896498&amp;all_sr_blocks=1403240101_422601059_4_0_0&amp;highlighted_blocks=1403240101_422601059_4_0_0&amp;matching_block_id=1403240101_422601059_4_0_0&amp;sr_pri_blocks=1403240101_422601059_4_0_0__2150280&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Gabi's Appartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/gabis-appartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=76&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1305827501_403419497_0_0_0&amp;highlighted_blocks=1305827501_403419497_0_0_0&amp;matching_block_id=1305827501_403419497_0_0_0&amp;sr_pri_blocks=1305827501_403419497_0_0_0__1793780&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pensiunea Warthe Bed &amp; Breakfast</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pensiunea-warthe-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=77&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=60537404_420938514_3_1_0&amp;highlighted_blocks=60537404_420938514_3_1_0&amp;matching_block_id=60537404_420938514_3_1_0&amp;sr_pri_blocks=60537404_420938514_3_1_0__3458400&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,584</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ada Homes 306</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ada-homes-306.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=78&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=987979601_372379867_3_0_0&amp;highlighted_blocks=987979601_372379867_3_0_0&amp;matching_block_id=987979601_372379867_3_0_0&amp;sr_pri_blocks=987979601_372379867_3_0_0__2233976&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>French Boutique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/holiday-villa.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=79&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=206903201_126031933_0_2_0&amp;highlighted_blocks=206903201_126031933_0_2_0&amp;matching_block_id=206903201_126031933_0_2_0&amp;sr_pri_blocks=206903201_126031933_0_2_0__3323214&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,232</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bada Bing Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pensiunea-bada-bing.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=80&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=690394808_285579983_0_0_0&amp;highlighted_blocks=690394808_285579983_0_0_0&amp;matching_block_id=690394808_285579983_0_0_0&amp;sr_pri_blocks=690394808_285579983_0_0_0__3042600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,426</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Friendly little studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/friendly-little-studio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=81&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1043001301_377147384_0_0_0&amp;highlighted_blocks=1043001301_377147384_0_0_0&amp;matching_block_id=1043001301_377147384_0_0_0&amp;sr_pri_blocks=1043001301_377147384_0_0_0__1609548&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,095</x:t>
+  </x:si>
+  <x:si>
+    <x:t>D&amp;C Apartament</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/d-amp-c-apartament.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=82&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=965447201_385311198_4_0_0&amp;highlighted_blocks=965447201_385311198_4_0_0&amp;matching_block_id=965447201_385311198_4_0_0&amp;sr_pri_blocks=965447201_385311198_4_0_0__4812600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48,126</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Mayona</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-mayona.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=83&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1541609001_426733488_3_0_0&amp;highlighted_blocks=1541609001_426733488_3_0_0&amp;matching_block_id=1541609001_426733488_3_0_0&amp;sr_pri_blocks=1541609001_426733488_3_0_0__1622670&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,227</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sun Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sun-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=84&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1245512801_396724713_0_0_0&amp;highlighted_blocks=1245512801_396724713_0_0_0&amp;matching_block_id=1245512801_396724713_0_0_0&amp;sr_pri_blocks=1245512801_396724713_0_0_0__6559650&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65,597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa 29</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casuta-centrala.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=85&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1221913101_394831208_4_0_0&amp;highlighted_blocks=1221913101_394831208_4_0_0&amp;matching_block_id=1221913101_394831208_4_0_0&amp;sr_pri_blocks=1221913101_394831208_4_0_0__1755600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,556</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Plermont Luxury Apartments Coresi Kasper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/plermont-luxury-apartments-kasper.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=86&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1361209101_408429922_3_0_0_826036&amp;highlighted_blocks=1361209101_408429922_3_0_0_826036&amp;matching_block_id=1361209101_408429922_3_0_0_826036&amp;sr_pri_blocks=1361209101_408429922_3_0_0_826036_3659040&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,590</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Signature Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-signature-collection.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=87&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1455967604_417071727_4_0_0&amp;highlighted_blocks=1455967604_417071727_4_0_0&amp;matching_block_id=1455967604_417071727_4_0_0&amp;sr_pri_blocks=1455967604_417071727_4_0_0__4333230&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Centru Vechi Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cazare-centru-vechi-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=88&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1486911501_420178318_3_0_0&amp;highlighted_blocks=1486911501_420178318_3_0_0&amp;matching_block_id=1486911501_420178318_3_0_0&amp;sr_pri_blocks=1486911501_420178318_3_0_0__2560140&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,601</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brașov Residential</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/brasov-residential-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=89&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1333868901_426404193_3_2_0&amp;highlighted_blocks=1333868901_426404193_3_2_0&amp;matching_block_id=1333868901_426404193_3_2_0&amp;sr_pri_blocks=1333868901_426404193_3_2_0__2533607&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Charm Old Town Accomodation</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/charm-old-city-studio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=90&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=678766601_277133650_3_0_0&amp;highlighted_blocks=678766601_277133650_3_0_0&amp;matching_block_id=678766601_277133650_3_0_0&amp;sr_pri_blocks=678766601_277133650_3_0_0__2625718&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,257</x:t>
+  </x:si>
+  <x:si>
+    <x:t>With a View Residence - Luxury Apartament - Panoramic view over the City</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartamente-rodiva-33.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=91&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=556841901_207253303_3_0_0&amp;highlighted_blocks=556841901_207253303_3_0_0&amp;matching_block_id=556841901_207253303_3_0_0&amp;sr_pri_blocks=556841901_207253303_3_0_0__7369160&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73,692</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Păltinel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/paltinel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=92&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1206302601_392846861_0_0_0&amp;highlighted_blocks=1206302601_392846861_0_0_0&amp;matching_block_id=1206302601_392846861_0_0_0&amp;sr_pri_blocks=1206302601_392846861_0_0_0__5529600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,296</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Pandora Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-pandora-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=93&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1430758102_414634262_4_0_0&amp;highlighted_blocks=1430758102_414634262_4_0_0&amp;matching_block_id=1430758102_414634262_4_0_0&amp;sr_pri_blocks=1430758102_414634262_4_0_0__2797021&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,970</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kasper Coresi Mall - Rise Private Apartments &amp; Suites</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/rise-apartments-kasper-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=94&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1048202207_377095828_3_0_0&amp;highlighted_blocks=1048202207_377095828_3_0_0&amp;matching_block_id=1048202207_377095828_3_0_0&amp;sr_pri_blocks=1048202207_377095828_3_0_0__4208100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,081</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ZiRa Residence - Authentic rooms in Old Town</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pan-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=95&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=827230506_424301215_3_0_0&amp;highlighted_blocks=827230506_424301215_3_0_0&amp;matching_block_id=827230506_424301215_3_0_0&amp;sr_pri_blocks=827230506_424301215_3_0_0__2884660&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,847</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ardor Apt - Bright and Secluded Apartment in the heart of Old Town</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ardor-apt-bright-and-secluded-apartment-in-the-heart-of-old-town.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=96&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=773983301_342168344_4_0_0&amp;highlighted_blocks=773983301_342168344_4_0_0&amp;matching_block_id=773983301_342168344_4_0_0&amp;sr_pri_blocks=773983301_342168344_4_0_0__2806570&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,066</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Plaza Alpine Escape Studio with Free Parking, Balcony, Washer &amp; Dryer</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/urban-plaza-mountain-view-alpine-escape-studio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=97&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1110369901_384752572_3_0_0&amp;highlighted_blocks=1110369901_384752572_3_0_0&amp;matching_block_id=1110369901_384752572_3_0_0&amp;sr_pri_blocks=1110369901_384752572_3_0_0__3836432&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38,364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartamente Olivero</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartamente-olivero.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=98&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=273492801_129797543_4_0_0&amp;highlighted_blocks=273492801_129797543_4_0_0&amp;matching_block_id=273492801_129797543_4_0_0&amp;sr_pri_blocks=273492801_129797543_4_0_0__2353692&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23,537</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Valentina's Flat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/valentina-39-s-flat.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=99&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=607068101_417575057_0_0_0&amp;highlighted_blocks=607068101_417575057_0_0_0&amp;matching_block_id=607068101_417575057_0_0_0&amp;sr_pri_blocks=607068101_417575057_0_0_0__3114969&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,150</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SB Nest Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sb-nest-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=100&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896501&amp;all_sr_blocks=1479163201_419381852_4_0_0&amp;highlighted_blocks=1479163201_419381852_4_0_0&amp;matching_block_id=1479163201_419381852_4_0_0&amp;sr_pri_blocks=1479163201_419381852_4_0_0__2211166&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,112</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartamentul 16</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartamentul-16.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=101&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=805862101_342009780_3_0_0&amp;highlighted_blocks=805862101_342009780_3_0_0&amp;matching_block_id=805862101_342009780_3_0_0&amp;sr_pri_blocks=805862101_342009780_3_0_0__2589840&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,898</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ALBERT RESIDENCE City Center Accommodation Brașov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/albert-residence-brasov4.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=102&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1498938001_424516903_3_2_0&amp;highlighted_blocks=1498938001_424516903_3_2_0&amp;matching_block_id=1498938001_424516903_3_2_0&amp;sr_pri_blocks=1498938001_424516903_3_2_0__5884344&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,843</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa MIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-mio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=103&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1541610501_425731194_4_0_0&amp;highlighted_blocks=1541610501_425731194_4_0_0&amp;matching_block_id=1541610501_425731194_4_0_0&amp;sr_pri_blocks=1541610501_425731194_4_0_0__1787849&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,878</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Central Delight</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/central-delight.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=104&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1445089201_415917974_3_0_0&amp;highlighted_blocks=1445089201_415917974_3_0_0&amp;matching_block_id=1445089201_415917974_3_0_0&amp;sr_pri_blocks=1445089201_415917974_3_0_0__4238550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,386</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Castel'or Residence - Deluxe Restored Apartment in the heart of Old Town with Unique Views of Tampa Mt</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/castel-or-residence-deluxe-restored-apartment-in-the-heart-of-old-town-with-uniq.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=105&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=809371601_342539098_3_0_0&amp;highlighted_blocks=809371601_342539098_3_0_0&amp;matching_block_id=809371601_342539098_3_0_0&amp;sr_pri_blocks=809371601_342539098_3_0_0__3510036&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament NORA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-leonora.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=106&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=199681104_350739713_0_0_0&amp;highlighted_blocks=199681104_350739713_0_0_0&amp;matching_block_id=199681104_350739713_0_0_0&amp;sr_pri_blocks=199681104_350739713_0_0_0__1871100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,711</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOOS Aparthotel Qualis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/moos-aparthotel-qualis.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=107&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1441131501_415559568_3_0_0&amp;highlighted_blocks=1441131501_415559568_3_0_0&amp;matching_block_id=1441131501_415559568_3_0_0&amp;sr_pri_blocks=1441131501_415559568_3_0_0__2762100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,621</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Family Crib</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-family-crib-brasov1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=108&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1099906901_382856437_5_0_0&amp;highlighted_blocks=1099906901_382856437_5_0_0&amp;matching_block_id=1099906901_382856437_5_0_0&amp;sr_pri_blocks=1099906901_382856437_5_0_0__2859490&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,595</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/grand.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=109&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=4127217_144025049_3_1_0&amp;highlighted_blocks=4127217_144025049_3_1_0&amp;matching_block_id=4127217_144025049_3_1_0&amp;sr_pri_blocks=4127217_144025049_3_1_0__4551520&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,515</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cabanute Luca Ama Bran</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cabanute-luca-ama-bran.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=110&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=695199902_405610914_4_0_0&amp;highlighted_blocks=695199902_405610914_4_0_0&amp;matching_block_id=695199902_405610914_4_0_0&amp;sr_pri_blocks=695199902_405610914_4_0_0__4070600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Old Citadel Hill Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/old-citadel-hill-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=111&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=737915701_361084842_0_0_0&amp;highlighted_blocks=737915701_361084842_0_0_0&amp;matching_block_id=737915701_361084842_0_0_0&amp;sr_pri_blocks=737915701_361084842_0_0_0__2909280&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,093</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Street</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-street.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=112&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1488540801_420416930_6_0_0&amp;highlighted_blocks=1488540801_420416930_6_0_0&amp;matching_block_id=1488540801_420416930_6_0_0&amp;sr_pri_blocks=1488540801_420416930_6_0_0__3963816&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,638</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa ta la munte</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-cu-2-camere-brasov2.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=113&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1070454701_384923956_5_0_0&amp;highlighted_blocks=1070454701_384923956_5_0_0&amp;matching_block_id=1070454701_384923956_5_0_0&amp;sr_pri_blocks=1070454701_384923956_5_0_0__2534104&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Apartment #CasaMihai Free Parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/modern-flat-opened-in-2022-great-for-4-people.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=114&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=912806601_362694911_0_0_0&amp;highlighted_blocks=912806601_362694911_0_0_0&amp;matching_block_id=912806601_362694911_0_0_0&amp;sr_pri_blocks=912806601_362694911_0_0_0__2803470&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,035</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Middle Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/middle-apartaments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=115&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1173866001_389964817_0_0_0&amp;highlighted_blocks=1173866001_389964817_0_0_0&amp;matching_block_id=1173866001_389964817_0_0_0&amp;sr_pri_blocks=1173866001_389964817_0_0_0__3030444&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vila Nicopole Art &amp; Wine</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/vila-nicopole.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=116&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=458076601_139620229_3_33_0&amp;highlighted_blocks=458076601_139620229_3_33_0&amp;matching_block_id=458076601_139620229_3_33_0&amp;sr_pri_blocks=458076601_139620229_3_33_0__3999600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>La Teatru - 2BD Apartment near Theatre and Old Town</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cali-2bd-apartment-near-theatre-and-old-town.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=117&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1283788201_401320775_4_0_0&amp;highlighted_blocks=1283788201_401320775_4_0_0&amp;matching_block_id=1283788201_401320775_4_0_0&amp;sr_pri_blocks=1283788201_401320775_4_0_0__3888660&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38,887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLH - The Modern Classic Romanian</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/traditional-meets-modern.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=118&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1226706701_394712860_3_0_0&amp;highlighted_blocks=1226706701_394712860_3_0_0&amp;matching_block_id=1226706701_394712860_3_0_0&amp;sr_pri_blocks=1226706701_394712860_3_0_0__2704480&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,045</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cozy Corner Guesthouse - Casa Centrul Civic si parcare</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cozy-corner-guesthouse.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=119&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1055378401_398415933_4_0_0&amp;highlighted_blocks=1055378401_398415933_4_0_0&amp;matching_block_id=1055378401_398415933_4_0_0&amp;sr_pri_blocks=1055378401_398415933_4_0_0__4283175&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,832</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AntraLux Central Suite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/antralux-central-suite.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=120&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1490605701_420724590_3_0_0&amp;highlighted_blocks=1490605701_420724590_3_0_0&amp;matching_block_id=1490605701_420724590_3_0_0&amp;sr_pri_blocks=1490605701_420724590_3_0_0__2361364&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23,614</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cosmo studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cosmo-studio-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=121&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1301982401_403078524_3_0_0&amp;highlighted_blocks=1301982401_403078524_3_0_0&amp;matching_block_id=1301982401_403078524_3_0_0&amp;sr_pri_blocks=1301982401_403078524_3_0_0__1733175&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,332</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Avram Iancu Private Apartment with AC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/schiller-residence-private-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=122&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=257076501_408526480_4_0_0&amp;highlighted_blocks=257076501_408526480_4_0_0&amp;matching_block_id=257076501_408526480_4_0_0&amp;sr_pri_blocks=257076501_408526480_4_0_0__2686088&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,861</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HOTEL BOUTIQUE CASA CHITIC -HOTEL AND RESTAURANT Str Johann Gott nr7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-chitic.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=123&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=356850201_131980679_0_1_0&amp;highlighted_blocks=356850201_131980679_0_1_0&amp;matching_block_id=356850201_131980679_0_1_0&amp;sr_pri_blocks=356850201_131980679_0_1_0__7009200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70,092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ada Homes 404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ada-homes-404.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=124&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1389641301_426482647_3_0_0&amp;highlighted_blocks=1389641301_426482647_3_0_0&amp;matching_block_id=1389641301_426482647_3_0_0&amp;sr_pri_blocks=1389641301_426482647_3_0_0__1941376&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,414</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casamigos Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casamigos-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=125&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896512&amp;all_sr_blocks=1520081701_423675432_3_0_0&amp;highlighted_blocks=1520081701_423675432_3_0_0&amp;matching_block_id=1520081701_423675432_3_0_0&amp;sr_pri_blocks=1520081701_423675432_3_0_0__2092958&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,930</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Castanilor 6 - Hip industrial apartment close to city centre</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/castanilor-6-hip-industrial-apartment-close-to-city-centre.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=126&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=890160901_359091191_3_0_0&amp;highlighted_blocks=890160901_359091191_3_0_0&amp;matching_block_id=890160901_359091191_3_0_0&amp;sr_pri_blocks=890160901_359091191_3_0_0__2971429&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,714</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skylark - Milano Studio with Terrace and Panoramic View</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sapphire-condo-with-mountain-view-amp-terrace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=127&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=888898501_360140489_3_0_0&amp;highlighted_blocks=888898501_360140489_3_0_0&amp;matching_block_id=888898501_360140489_3_0_0&amp;sr_pri_blocks=888898501_360140489_3_0_0__2970000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Hills Loft</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/urban-hills-loft-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=128&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1548940701_426123940_4_0_0&amp;highlighted_blocks=1548940701_426123940_4_0_0&amp;matching_block_id=1548940701_426123940_4_0_0&amp;sr_pri_blocks=1548940701_426123940_4_0_0__2040570&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quiboo #4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/quiboo-3-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=129&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=651371401_266132108_3_0_0_265017&amp;highlighted_blocks=651371401_266132108_3_0_0_265017&amp;matching_block_id=651371401_266132108_3_0_0_265017&amp;sr_pri_blocks=651371401_266132108_3_0_0_265017_3911016&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Split Crib | Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/split-crib.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=130&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=794130901_424459955_3_0_0&amp;highlighted_blocks=794130901_424459955_3_0_0&amp;matching_block_id=794130901_424459955_3_0_0&amp;sr_pri_blocks=794130901_424459955_3_0_0__2682507&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26,825</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Carolina Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-carolina-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=131&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=489413601_233739468_3_0_0&amp;highlighted_blocks=489413601_233739468_3_0_0&amp;matching_block_id=489413601_233739468_3_0_0&amp;sr_pri_blocks=489413601_233739468_3_0_0__6087600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60,876</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Deluxe Suite Coresi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/coresi-suits.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=132&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=588001501_402685919_4_0_0&amp;highlighted_blocks=588001501_402685919_4_0_0&amp;matching_block_id=588001501_402685919_4_0_0&amp;sr_pri_blocks=588001501_402685919_4_0_0__2469436&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,694</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament Piata Sfatului</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-casa-mandl.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=133&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=198492301_329620677_5_0_0&amp;highlighted_blocks=198492301_329620677_5_0_0&amp;matching_block_id=198492301_329620677_5_0_0&amp;sr_pri_blocks=198492301_329620677_5_0_0__5529600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ada Homes B76</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ada-homes-b76.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=134&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1110548501_384037919_3_0_0&amp;highlighted_blocks=1110548501_384037919_3_0_0&amp;matching_block_id=1110548501_384037919_3_0_0&amp;sr_pri_blocks=1110548501_384037919_3_0_0__1889366&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,894</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament Roza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-roza.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=135&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=48172901_329739760_3_0_0&amp;highlighted_blocks=48172901_329739760_3_0_0&amp;matching_block_id=48172901_329739760_3_0_0&amp;sr_pri_blocks=48172901_329739760_3_0_0__1631400&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,314</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Patrick</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/patrick.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=136&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1360264201_410023776_4_0_0&amp;highlighted_blocks=1360264201_410023776_4_0_0&amp;matching_block_id=1360264201_410023776_4_0_0&amp;sr_pri_blocks=1360264201_410023776_4_0_0__1866110&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,661</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CORESI 3 CAMERE TOP CITY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/coresi-3-camere-top-city.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=137&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1179371901_425063466_6_0_0&amp;highlighted_blocks=1179371901_425063466_6_0_0&amp;matching_block_id=1179371901_425063466_6_0_0&amp;sr_pri_blocks=1179371901_425063466_6_0_0__4950850&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Plaza Mountain View Luxury Retreat</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/urban-plaza-mountain-view-luxury-retreat-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=138&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1070164001_400495666_3_0_0&amp;highlighted_blocks=1070164001_400495666_3_0_0&amp;matching_block_id=1070164001_400495666_3_0_0&amp;sr_pri_blocks=1070164001_400495666_3_0_0__4962040&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,620</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Commodores Quarters</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/commodores-quarters.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=139&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=598806901_273191064_3_0_0&amp;highlighted_blocks=598806901_273191064_3_0_0&amp;matching_block_id=598806901_273191064_3_0_0&amp;sr_pri_blocks=598806901_273191064_3_0_0__2560140&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>M&amp;F Apartment EMINESCU</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/m-amp-f-apartment-eminescu.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=140&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1326442701_406851515_0_0_0&amp;highlighted_blocks=1326442701_406851515_0_0_0&amp;matching_block_id=1326442701_406851515_0_0_0&amp;sr_pri_blocks=1326442701_406851515_0_0_0__4164600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41,646</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Shay Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-shay-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=141&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1549322901_426158771_0_0_0&amp;highlighted_blocks=1549322901_426158771_0_0_0&amp;matching_block_id=1549322901_426158771_0_0_0&amp;sr_pri_blocks=1549322901_426158771_0_0_0__1581565&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>15,816</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Victoriei Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/victoriei-residence-brasov1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=142&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=1476132001_419052030_5_0_0&amp;highlighted_blocks=1476132001_419052030_5_0_0&amp;matching_block_id=1476132001_419052030_5_0_0&amp;sr_pri_blocks=1476132001_419052030_5_0_0__4517010&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Elizabeth Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/elizabeth-apartment-historical-center.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=143&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=649613901_265945848_3_0_0&amp;highlighted_blocks=649613901_265945848_3_0_0&amp;matching_block_id=649613901_265945848_3_0_0&amp;sr_pri_blocks=649613901_265945848_3_0_0__2150280&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Quiboo #3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/quiboo-3-brasov1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=144&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896522&amp;all_sr_blocks=835568601_348984619_0_0_0_265018&amp;highlighted_blocks=835568601_348984619_0_0_0_265018&amp;matching_block_id=835568601_348984619_0_0_0_265018&amp;sr_pri_blocks=835568601_348984619_0_0_0_265018_2822616&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ariel Deluxe Apartment - Balcony &amp; Free Parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ariel-apartments-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=145&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896523&amp;all_sr_blocks=1249663701_397547448_0_0_0&amp;highlighted_blocks=1249663701_397547448_0_0_0&amp;matching_block_id=1249663701_397547448_0_0_0&amp;sr_pri_blocks=1249663701_397547448_0_0_0__2117712&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,177</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aly Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/aly-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=146&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896523&amp;all_sr_blocks=1143731901_387222742_4_0_0&amp;highlighted_blocks=1143731901_387222742_4_0_0&amp;matching_block_id=1143731901_387222742_4_0_0&amp;sr_pri_blocks=1143731901_387222742_4_0_0__1919997&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Belle Époque Apartament</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/belle-epoque-apartament.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=147&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896523&amp;all_sr_blocks=1328287801_405411280_3_0_0&amp;highlighted_blocks=1328287801_405411280_3_0_0&amp;matching_block_id=1328287801_405411280_3_0_0&amp;sr_pri_blocks=1328287801_405411280_3_0_0__2919036&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,190</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Barok Appart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/barok-appart.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=148&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896523&amp;all_sr_blocks=951916701_367780903_5_0_0&amp;highlighted_blocks=951916701_367780903_5_0_0&amp;matching_block_id=951916701_367780903_5_0_0&amp;sr_pri_blocks=951916701_367780903_5_0_0__4015600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Muresenilor Central Residence Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/muresenilor-central-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=149&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896523&amp;all_sr_blocks=1375250201_416569462_3_0_0&amp;highlighted_blocks=1375250201_416569462_3_0_0&amp;matching_block_id=1375250201_416569462_3_0_0&amp;sr_pri_blocks=1375250201_416569462_3_0_0__4211000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,110</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ASM Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/asm-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=150&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896523&amp;all_sr_blocks=1289916601_402744432_3_0_0&amp;highlighted_blocks=1289916601_402744432_3_0_0&amp;matching_block_id=1289916601_402744432_3_0_0&amp;sr_pri_blocks=1289916601_402744432_3_0_0__3546100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35,461</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amasi Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/amasi-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=151&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1454734001_416792067_3_0_0&amp;highlighted_blocks=1454734001_416792067_3_0_0&amp;matching_block_id=1454734001_416792067_3_0_0&amp;sr_pri_blocks=1454734001_416792067_3_0_0__2818200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,182</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dream Apartments Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/dreamapartmentsbrasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=152&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=401717902_190922978_4_0_0&amp;highlighted_blocks=401717902_190922978_4_0_0&amp;matching_block_id=401717902_190922978_4_0_0&amp;sr_pri_blocks=401717902_190922978_4_0_0__2421440&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bella Vista Green Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/bella-vista-green-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=153&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1349087901_407247792_3_0_0&amp;highlighted_blocks=1349087901_407247792_3_0_0&amp;matching_block_id=1349087901_407247792_3_0_0&amp;sr_pri_blocks=1349087901_407247792_3_0_0__2409612&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,096</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand View Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/grand-view-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=154&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=281927801_275675601_4_0_0&amp;highlighted_blocks=281927801_275675601_4_0_0&amp;matching_block_id=281927801_275675601_4_0_0&amp;sr_pri_blocks=281927801_275675601_4_0_0__4073400&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,734</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brasov centrul vechi - 67sqm - 2min to Counsel Square</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/old-town-muresenilor-2-min-away-from-counsel-square.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=155&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=580315301_225425894_3_0_0_1105489&amp;highlighted_blocks=580315301_225425894_3_0_0_1105489&amp;matching_block_id=580315301_225425894_3_0_0_1105489&amp;sr_pri_blocks=580315301_225425894_3_0_0_1105489_4001373&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ada Homes Coresi 706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ada-homes-coresi-706.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=156&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1079278701_420817679_3_0_0&amp;highlighted_blocks=1079278701_420817679_3_0_0&amp;matching_block_id=1079278701_420817679_3_0_0&amp;sr_pri_blocks=1079278701_420817679_3_0_0__2256345&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,563</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SWEET HOUSES VILLa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sweet-houses-vila.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=157&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=672813101_379475715_10_0_0&amp;highlighted_blocks=672813101_379475715_10_0_0&amp;matching_block_id=672813101_379475715_10_0_0&amp;sr_pri_blocks=672813101_379475715_10_0_0__9477600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94,776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Vila Ekooos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/vila-ekooos.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=158&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=481479601_155371786_0_0_0&amp;highlighted_blocks=481479601_155371786_0_0_0&amp;matching_block_id=481479601_155371786_0_0_0&amp;sr_pri_blocks=481479601_155371786_0_0_0__5248800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52,488</x:t>
+  </x:si>
+  <x:si>
+    <x:t>City Center nr 5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/city-center-nr-5.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=159&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1236229801_406984445_3_0_0&amp;highlighted_blocks=1236229801_406984445_3_0_0&amp;matching_block_id=1236229801_406984445_3_0_0&amp;sr_pri_blocks=1236229801_406984445_3_0_0__2332440&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23,324</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5th Floor Executive Apartment with Balcony and Free Parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/5thfloor-executive-apart-wbalcony-amp-free-parking.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=160&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1069063401_407890109_3_0_0&amp;highlighted_blocks=1069063401_407890109_3_0_0&amp;matching_block_id=1069063401_407890109_3_0_0&amp;sr_pri_blocks=1069063401_407890109_3_0_0__5050512&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50,505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sona Plus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sona-plus.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=161&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1071213801_379638450_3_0_0&amp;highlighted_blocks=1071213801_379638450_3_0_0&amp;matching_block_id=1071213801_379638450_3_0_0&amp;sr_pri_blocks=1071213801_379638450_3_0_0__2773844&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,738</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APARTAMENT JOHANN GOTT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-johann-gott-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=162&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=483223701_157095983_0_0_0&amp;highlighted_blocks=483223701_157095983_0_0_0&amp;matching_block_id=483223701_157095983_0_0_0&amp;sr_pri_blocks=483223701_157095983_0_0_0__4989600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,896</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luna Studio - Free parking &amp; mountain view</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/luna-studio-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=163&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1489234701_420573084_3_0_0&amp;highlighted_blocks=1489234701_420573084_3_0_0&amp;matching_block_id=1489234701_420573084_3_0_0&amp;sr_pri_blocks=1489234701_420573084_3_0_0__2223335&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,233</x:t>
+  </x:si>
+  <x:si>
+    <x:t>John Residence Central Apartament Private Parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/john-residence-central-apartament-private-parking.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=164&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1353553201_407686726_3_0_0&amp;highlighted_blocks=1353553201_407686726_3_0_0&amp;matching_block_id=1353553201_407686726_3_0_0&amp;sr_pri_blocks=1353553201_407686726_3_0_0__2792394&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,924</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mountain View Terrace Oasis with Parking and AC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/mountain-view-terrace-oasis.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=165&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1265934801_407889952_3_0_0&amp;highlighted_blocks=1265934801_407889952_3_0_0&amp;matching_block_id=1265934801_407889952_3_0_0&amp;sr_pri_blocks=1265934801_407889952_3_0_0__5131184&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51,312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brasov Hillside Suite Near City Center</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/brasov-hillside-ii-apartment-near-city-center.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=166&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1455415001_423662278_0_0_0&amp;highlighted_blocks=1455415001_423662278_0_0_0&amp;matching_block_id=1455415001_423662278_0_0_0&amp;sr_pri_blocks=1455415001_423662278_0_0_0__2564813&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,648</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nobless Boutique Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/noblessresidence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=167&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=934538202_370811926_3_0_0&amp;highlighted_blocks=934538202_370811926_3_0_0&amp;matching_block_id=934538202_370811926_3_0_0&amp;sr_pri_blocks=934538202_370811926_3_0_0__3186000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,860</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Golden Time Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/golden-time.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=168&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=46010206_126031212_3_1_0_1102803&amp;highlighted_blocks=46010206_126031212_3_1_0_1102803&amp;matching_block_id=46010206_126031212_3_1_0_1102803&amp;sr_pri_blocks=46010206_126031212_3_1_0_1102803_8910000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>89,100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartments for rent near Coresi Shopping</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/lcb-studio-nl11.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=169&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1509858705_423716563_3_0_0&amp;highlighted_blocks=1509858705_423716563_3_0_0&amp;matching_block_id=1509858705_423716563_3_0_0&amp;sr_pri_blocks=1509858705_423716563_3_0_0__1792692&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,927</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Dimitrie Cantemir Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/dimitrie-cantemir-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=170&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=497439001_172810782_3_0_0&amp;highlighted_blocks=497439001_172810782_3_0_0&amp;matching_block_id=497439001_172810782_3_0_0&amp;sr_pri_blocks=497439001_172810782_3_0_0__2047020&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,470</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ada Homes Coresi 202</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ada-homes-coresi-202.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=171&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1208109401_392989438_4_0_0&amp;highlighted_blocks=1208109401_392989438_4_0_0&amp;matching_block_id=1208109401_392989438_4_0_0&amp;sr_pri_blocks=1208109401_392989438_4_0_0__2423658&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,237</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament Roma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-roma-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=172&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=693165801_285385556_3_0_0&amp;highlighted_blocks=693165801_285385556_3_0_0&amp;matching_block_id=693165801_285385556_3_0_0&amp;sr_pri_blocks=693165801_285385556_3_0_0__2970000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cosy home in the heart of Old Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cosy-home-in-the-heart-of-old-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=173&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1175240801_390073491_3_0_0&amp;highlighted_blocks=1175240801_390073491_3_0_0&amp;matching_block_id=1175240801_390073491_3_0_0&amp;sr_pri_blocks=1175240801_390073491_3_0_0__2123866&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,239</x:t>
+  </x:si>
+  <x:si>
+    <x:t>La Dolce Vita Central</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/la-dolce-vita-central.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=174&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1415864003_413286899_3_2_0&amp;highlighted_blocks=1415864003_413286899_3_2_0&amp;matching_block_id=1415864003_413286899_3_2_0&amp;sr_pri_blocks=1415864003_413286899_3_2_0__2283242&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,832</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Galactic&amp;Ludmila Suite SPA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/galactic.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=175&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896533&amp;all_sr_blocks=1302600002_407157935_3_1_0&amp;highlighted_blocks=1302600002_407157935_3_1_0&amp;matching_block_id=1302600002_407157935_3_1_0&amp;sr_pri_blocks=1302600002_407157935_3_1_0__6177600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61,776</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Versus Art Studio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/versus-art-studio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=176&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=33790801_126030839_3_0_0&amp;highlighted_blocks=33790801_126030839_3_0_0&amp;matching_block_id=33790801_126030839_3_0_0&amp;sr_pri_blocks=33790801_126030839_3_0_0__2193797&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,938</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Prestige Apart Complex Uno Residence</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/prestige-apart-complex-uno-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=177&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1094259401_382338856_0_0_0&amp;highlighted_blocks=1094259401_382338856_0_0_0&amp;matching_block_id=1094259401_382338856_0_0_0&amp;sr_pri_blocks=1094259401_382338856_0_0_0__4833730&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>48,337</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOOS Apartment CORESI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/moos-apartment-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=178&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1510502101_422811253_3_0_0&amp;highlighted_blocks=1510502101_422811253_3_0_0&amp;matching_block_id=1510502101_422811253_3_0_0&amp;sr_pri_blocks=1510502101_422811253_3_0_0__2509650&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,097</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Retreat in the city</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/retreat-in-the-city-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=179&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1457305202_423794482_3_0_0&amp;highlighted_blocks=1457305202_423794482_3_0_0&amp;matching_block_id=1457305202_423794482_3_0_0&amp;sr_pri_blocks=1457305202_423794482_3_0_0__2095632&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,956</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Anca Boutique Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pensiunea-casa-anca.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=180&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=34703003_214471260_0_0_0&amp;highlighted_blocks=34703003_214471260_0_0_0&amp;matching_block_id=34703003_214471260_0_0_0&amp;sr_pri_blocks=34703003_214471260_0_0_0__8256600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>82,566</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Schloss Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/schloss-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=181&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=804575201_341854965_3_0_0_427337&amp;highlighted_blocks=804575201_341854965_3_0_0_427337&amp;matching_block_id=804575201_341854965_3_0_0_427337&amp;sr_pri_blocks=804575201_341854965_3_0_0_427337_3024648&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,246</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nobel Stay Coresi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/nobel-stay-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=182&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1529779201_424523328_4_0_0&amp;highlighted_blocks=1529779201_424523328_4_0_0&amp;matching_block_id=1529779201_424523328_4_0_0&amp;sr_pri_blocks=1529779201_424523328_4_0_0__2417850&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,179</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coresi Comfort Suite</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/coresi-comfort-suite.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=183&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1528513601_424417019_3_0_0&amp;highlighted_blocks=1528513601_424417019_3_0_0&amp;matching_block_id=1528513601_424417019_3_0_0&amp;sr_pri_blocks=1528513601_424417019_3_0_0__3143052&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,431</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ada Homes Coresi 707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ada-homes-coresi-707.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=184&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1079447301_405490335_4_0_0&amp;highlighted_blocks=1079447301_405490335_4_0_0&amp;matching_block_id=1079447301_405490335_4_0_0&amp;sr_pri_blocks=1079447301_405490335_4_0_0__2515621&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,156</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament C&amp;L</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-c-amp-l-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=185&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=852575901_352635772_4_0_0&amp;highlighted_blocks=852575901_352635772_4_0_0&amp;matching_block_id=852575901_352635772_4_0_0&amp;sr_pri_blocks=852575901_352635772_4_0_0__1755600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4FriendsCoresiBrasov Pth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/4friendscoresibrasov-pth.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=186&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1378681901_409992255_4_0_0_1210723&amp;highlighted_blocks=1378681901_409992255_4_0_0_1210723&amp;matching_block_id=1378681901_409992255_4_0_0_1210723&amp;sr_pri_blocks=1378681901_409992255_4_0_0_1210723_10395000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>103,950</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AKI GRAY Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/aki-gray-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=187&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=496734903_406989102_0_0_0&amp;highlighted_blocks=496734903_406989102_0_0_0&amp;matching_block_id=496734903_406989102_0_0_0&amp;sr_pri_blocks=496734903_406989102_0_0_0__3386955&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,870</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blue Jay's Nest — AC &amp; Stylish Terrace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/blue-jays-nest-with-ac-and-stylish-terrace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=188&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1306471101_403471337_3_0_0&amp;highlighted_blocks=1306471101_403471337_3_0_0&amp;matching_block_id=1306471101_403471337_3_0_0&amp;sr_pri_blocks=1306471101_403471337_3_0_0__2933614&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>29,336</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4FriendsBrasov K7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/4friendsbrasov-k7.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=189&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1330381001_405581658_4_0_0_1210730&amp;highlighted_blocks=1330381001_405581658_4_0_0_1210730&amp;matching_block_id=1330381001_405581658_4_0_0_1210730&amp;sr_pri_blocks=1330381001_405581658_4_0_0_1210730_10395000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FLH - Coresi Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/flh-coresi-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=190&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1449980601_416370585_4_0_0&amp;highlighted_blocks=1449980601_416370585_4_0_0&amp;matching_block_id=1449980601_416370585_4_0_0&amp;sr_pri_blocks=1449980601_416370585_4_0_0__2270608&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,706</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nido Uno Brașov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/nido-uno-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=191&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1455965501_416895949_3_0_0&amp;highlighted_blocks=1455965501_416895949_3_0_0&amp;matching_block_id=1455965501_416895949_3_0_0&amp;sr_pri_blocks=1455965501_416895949_3_0_0__2420304&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frapin House</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pensiunea-casa-luka-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=192&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=746815903_421847225_0_0_0_1160843&amp;highlighted_blocks=746815903_421847225_0_0_0_1160843&amp;matching_block_id=746815903_421847225_0_0_0_1160843&amp;sr_pri_blocks=746815903_421847225_0_0_0_1160843_14137600&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>141,376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament Brown Gem Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-brown-gem-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=193&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=735279501_368291373_3_0_0&amp;highlighted_blocks=735279501_368291373_3_0_0&amp;matching_block_id=735279501_368291373_3_0_0&amp;sr_pri_blocks=735279501_368291373_3_0_0__1968120&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,681</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luxury Brasov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/luxury-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=194&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=288286901_126040134_3_0_0&amp;highlighted_blocks=288286901_126040134_3_0_0&amp;matching_block_id=288286901_126040134_3_0_0&amp;sr_pri_blocks=288286901_126040134_3_0_0__8830800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>88,308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4FriendsCoresiBrasov C</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/4friendscoresibrasov-c.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=195&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1197217601_392017165_4_0_0_1210743&amp;highlighted_blocks=1197217601_392017165_4_0_0_1210743&amp;matching_block_id=1197217601_392017165_4_0_0_1210743&amp;sr_pri_blocks=1197217601_392017165_4_0_0_1210743_4752000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>47,520</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arté - 2 Bedroom Apartment near Coresi Mall with Free Parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/arte-2-bedroom-apartment-near-coresi-mall-with-free-parking.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=196&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1062439101_378583799_3_0_0&amp;highlighted_blocks=1062439101_378583799_3_0_0&amp;matching_block_id=1062439101_378583799_3_0_0&amp;sr_pri_blocks=1062439101_378583799_3_0_0__2798569&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,986</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Eden Apartment With Free Private Parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/eden-apartment-with-free-private-parking.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=197&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1549476501_426169289_3_0_0&amp;highlighted_blocks=1549476501_426169289_3_0_0&amp;matching_block_id=1549476501_426169289_3_0_0&amp;sr_pri_blocks=1549476501_426169289_3_0_0__4942080&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>49,421</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4FriendsCoresiBrasov T</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/4friendscoresibrasov-t.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=198&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1058435801_378091621_4_0_0_1210745&amp;highlighted_blocks=1058435801_378091621_4_0_0_1210745&amp;matching_block_id=1058435801_378091621_4_0_0_1210745&amp;sr_pri_blocks=1058435801_378091621_4_0_0_1210745_10959300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109,593</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APARTAMENT AVANGARDEN EMA VERDE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-avangarden-ema-verde.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=199&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=688340401_279537133_3_0_0&amp;highlighted_blocks=688340401_279537133_3_0_0&amp;matching_block_id=688340401_279537133_3_0_0&amp;sr_pri_blocks=688340401_279537133_3_0_0__2013660&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ada Homes 02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/ada-homes-02.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKc6__KBsACAdICJDRmMzlhODYwLWNjMjgtNDc4MS05N2UzLTE4YWU0Njk0MjJmZdgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=200&amp;sr_order=popularity&amp;srpvid=557a998eebf2c04476815990e727e2f4&amp;srepoch=1767896544&amp;all_sr_blocks=1444014501_415833930_4_0_0&amp;highlighted_blocks=1444014501_415833930_4_0_0&amp;matching_block_id=1444014501_415833930_4_0_0&amp;sr_pri_blocks=1444014501_415833930_4_0_0__2712860&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27,129</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -658,7 +2236,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C26"/>
+  <x:dimension ref="A1:D26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -677,58 +2255,58 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>4</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
@@ -736,220 +2314,220 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>25</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>26</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="C16" s="0" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C16" s="0" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
         <x:v>68</x:v>
@@ -957,86 +2535,2522 @@
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>82</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
         <x:v>89</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4">
+      <x:c r="A53" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4">
+      <x:c r="A54" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:4">
+      <x:c r="A55" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:4">
+      <x:c r="A56" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:4">
+      <x:c r="A57" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:4">
+      <x:c r="A58" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D58" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:4">
+      <x:c r="A59" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:4">
+      <x:c r="A60" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:4">
+      <x:c r="A61" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:4">
+      <x:c r="A62" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:4">
+      <x:c r="A63" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:4">
+      <x:c r="A64" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:4">
+      <x:c r="A65" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:4">
+      <x:c r="A66" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:4">
+      <x:c r="A67" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:4">
+      <x:c r="A68" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:4">
+      <x:c r="A69" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:4">
+      <x:c r="A70" s="0" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:4">
+      <x:c r="A71" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:4">
+      <x:c r="A72" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:4">
+      <x:c r="A73" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:4">
+      <x:c r="A74" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:4">
+      <x:c r="A75" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:4">
+      <x:c r="A76" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:4">
+      <x:c r="A77" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:4">
+      <x:c r="A78" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:4">
+      <x:c r="A79" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:4">
+      <x:c r="A80" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:4">
+      <x:c r="A81" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:4">
+      <x:c r="A82" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:4">
+      <x:c r="A83" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:4">
+      <x:c r="A84" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:4">
+      <x:c r="A85" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:4">
+      <x:c r="A86" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:4">
+      <x:c r="A87" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:4">
+      <x:c r="A88" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:4">
+      <x:c r="A89" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:4">
+      <x:c r="A90" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:4">
+      <x:c r="A91" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:4">
+      <x:c r="A92" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:4">
+      <x:c r="A93" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:4">
+      <x:c r="A94" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:4">
+      <x:c r="A95" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:4">
+      <x:c r="A96" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:4">
+      <x:c r="A97" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:4">
+      <x:c r="A98" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:4">
+      <x:c r="A99" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:4">
+      <x:c r="A100" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:4">
+      <x:c r="A101" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:4">
+      <x:c r="A102" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:4">
+      <x:c r="A103" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:4">
+      <x:c r="A104" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:4">
+      <x:c r="A105" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:4">
+      <x:c r="A106" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:4">
+      <x:c r="A107" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:4">
+      <x:c r="A108" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:4">
+      <x:c r="A109" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:4">
+      <x:c r="A110" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:4">
+      <x:c r="A111" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:4">
+      <x:c r="A112" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:4">
+      <x:c r="A113" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:4">
+      <x:c r="A114" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:4">
+      <x:c r="A115" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:4">
+      <x:c r="A116" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:4">
+      <x:c r="A117" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:4">
+      <x:c r="A118" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:4">
+      <x:c r="A119" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:4">
+      <x:c r="A120" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:4">
+      <x:c r="A121" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:4">
+      <x:c r="A122" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:4">
+      <x:c r="A123" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:4">
+      <x:c r="A124" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:4">
+      <x:c r="A125" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:4">
+      <x:c r="A126" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:4">
+      <x:c r="A127" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:4">
+      <x:c r="A128" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:4">
+      <x:c r="A129" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:4">
+      <x:c r="A130" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:4">
+      <x:c r="A131" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:4">
+      <x:c r="A132" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:4">
+      <x:c r="A133" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:4">
+      <x:c r="A134" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:4">
+      <x:c r="A135" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:4">
+      <x:c r="A136" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:4">
+      <x:c r="A137" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:4">
+      <x:c r="A138" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:4">
+      <x:c r="A139" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:4">
+      <x:c r="A140" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:4">
+      <x:c r="A141" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:4">
+      <x:c r="A142" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:4">
+      <x:c r="A143" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:4">
+      <x:c r="A144" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:4">
+      <x:c r="A145" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:4">
+      <x:c r="A146" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:4">
+      <x:c r="A147" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:4">
+      <x:c r="A148" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:4">
+      <x:c r="A149" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:4">
+      <x:c r="A150" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:4">
+      <x:c r="A151" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:4">
+      <x:c r="A152" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:4">
+      <x:c r="A153" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:4">
+      <x:c r="A154" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:4">
+      <x:c r="A155" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:4">
+      <x:c r="A156" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:4">
+      <x:c r="A157" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:4">
+      <x:c r="A158" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:4">
+      <x:c r="A159" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:4">
+      <x:c r="A160" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:4">
+      <x:c r="A161" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:4">
+      <x:c r="A162" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:4">
+      <x:c r="A163" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:4">
+      <x:c r="A164" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:4">
+      <x:c r="A165" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:4">
+      <x:c r="A166" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:4">
+      <x:c r="A167" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:4">
+      <x:c r="A168" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:4">
+      <x:c r="A169" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:4">
+      <x:c r="A170" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:4">
+      <x:c r="A171" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:4">
+      <x:c r="A172" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:4">
+      <x:c r="A173" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:4">
+      <x:c r="A174" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:4">
+      <x:c r="A175" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:4">
+      <x:c r="A176" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:4">
+      <x:c r="A177" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:4">
+      <x:c r="A178" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:4">
+      <x:c r="A179" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:4">
+      <x:c r="A180" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:4">
+      <x:c r="A181" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:4">
+      <x:c r="A182" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:4">
+      <x:c r="A183" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:4">
+      <x:c r="A184" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:4">
+      <x:c r="A185" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:4">
+      <x:c r="A186" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:4">
+      <x:c r="A187" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:4">
+      <x:c r="A188" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:4">
+      <x:c r="A189" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:4">
+      <x:c r="A190" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:4">
+      <x:c r="A191" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:4">
+      <x:c r="A192" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:4">
+      <x:c r="A193" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:4">
+      <x:c r="A194" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:4">
+      <x:c r="A195" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:4">
+      <x:c r="A196" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:4">
+      <x:c r="A197" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:4">
+      <x:c r="A198" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="199" spans="1:4">
+      <x:c r="A199" s="0" t="s">
+        <x:v>615</x:v>
+      </x:c>
+      <x:c r="B199" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="C199" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="D199" s="0" t="s">
+        <x:v>617</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="200" spans="1:4">
+      <x:c r="A200" s="0" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B200" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C200" s="0" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="D200" s="0" t="s">
+        <x:v>620</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="201" spans="1:4">
+      <x:c r="A201" s="0" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="B201" s="0" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="C201" s="0" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D201" s="0" t="s">
+        <x:v>623</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
